--- a/output/pdf_financials_xlsx/BUFF.xlsx
+++ b/output/pdf_financials_xlsx/BUFF.xlsx
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.001453</v>
       </c>
     </row>
     <row r="35">
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.001453</v>
       </c>
     </row>
     <row r="37">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.001453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">

--- a/output/pdf_financials_xlsx/BUFF.xlsx
+++ b/output/pdf_financials_xlsx/BUFF.xlsx
@@ -2671,7 +2671,11 @@
           <t>Proceeds from private placement 7,781,042</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
